--- a/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_2368_completo.xlsx
+++ b/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_2368_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R7c0a0879740f4c40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R33c5317b087e474c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_2368_completo.xlsx
+++ b/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_2368_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R33c5317b087e474c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R677474882bc244e4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,36 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     60.1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>02/09/2025</x:t>
         </x:is>
       </x:c>
